--- a/artfynd/A 24747-2025 artfynd.xlsx
+++ b/artfynd/A 24747-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121551323</v>
+        <v>121551885</v>
       </c>
       <c r="B2" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510197</v>
+        <v>510175</v>
       </c>
       <c r="R2" t="n">
-        <v>6940458</v>
+        <v>6940616</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,53 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121551318</v>
+        <v>122277211</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andersmyren, Jmt</t>
+          <t>Anderstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510235</v>
+        <v>510421</v>
       </c>
       <c r="R3" t="n">
-        <v>6940512</v>
+        <v>6940342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,34 +855,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121551869</v>
+        <v>121551262</v>
       </c>
       <c r="B4" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,10 +911,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510142</v>
+        <v>510294</v>
       </c>
       <c r="R4" t="n">
-        <v>6940672</v>
+        <v>6940327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121551885</v>
+        <v>121551267</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1012,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510175</v>
+        <v>510293</v>
       </c>
       <c r="R5" t="n">
-        <v>6940616</v>
+        <v>6940355</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,15 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121551883</v>
+        <v>121551307</v>
       </c>
       <c r="B6" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510175</v>
+        <v>510271</v>
       </c>
       <c r="R6" t="n">
-        <v>6940616</v>
+        <v>6940417</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121551875</v>
+        <v>121551310</v>
       </c>
       <c r="B7" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510146</v>
+        <v>510284</v>
       </c>
       <c r="R7" t="n">
-        <v>6940658</v>
+        <v>6940426</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121551307</v>
+        <v>121551318</v>
       </c>
       <c r="B8" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510271</v>
+        <v>510235</v>
       </c>
       <c r="R8" t="n">
-        <v>6940417</v>
+        <v>6940512</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,15 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121551267</v>
+        <v>121551323</v>
       </c>
       <c r="B9" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510293</v>
+        <v>510197</v>
       </c>
       <c r="R9" t="n">
-        <v>6940355</v>
+        <v>6940458</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,15 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121551310</v>
+        <v>121551327</v>
       </c>
       <c r="B10" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1517,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510284</v>
+        <v>510178</v>
       </c>
       <c r="R10" t="n">
-        <v>6940426</v>
+        <v>6940499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,15 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121551262</v>
+        <v>121551869</v>
       </c>
       <c r="B11" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510294</v>
+        <v>510142</v>
       </c>
       <c r="R11" t="n">
-        <v>6940327</v>
+        <v>6940672</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,15 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121551881</v>
+        <v>121551875</v>
       </c>
       <c r="B12" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,10 +1719,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510148</v>
+        <v>510146</v>
       </c>
       <c r="R12" t="n">
-        <v>6940596</v>
+        <v>6940658</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,12 +1785,7 @@
         <v>121551879</v>
       </c>
       <c r="B13" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,15 +1883,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121551327</v>
+        <v>121551881</v>
       </c>
       <c r="B14" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,10 +1921,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510178</v>
+        <v>510148</v>
       </c>
       <c r="R14" t="n">
-        <v>6940499</v>
+        <v>6940596</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,6 +1981,107 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121551883</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Andersmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>510175</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6940616</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
